--- a/تهیه کارنامه ۳ ماهه نواحی.xlsx
+++ b/تهیه کارنامه ۳ ماهه نواحی.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U62"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="144" customWidth="1" min="1" max="1"/>
@@ -578,9 +578,10 @@
     <col width="38" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="32" customWidth="1" min="19" max="19"/>
-    <col width="43" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="107" customWidth="1" min="19" max="19"/>
+    <col width="127" customWidth="1" min="20" max="20"/>
+    <col width="43" customWidth="1" min="21" max="21"/>
+    <col width="53" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,6 +597,33 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
@@ -689,7 +717,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>میانگین درصد تحقق</t>
+          <t>درصد تحقق وزنی اهداف</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -700,6 +728,11 @@
       <c r="U30" s="3" t="inlineStr">
         <is>
           <t>رتبه استانی</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>سطح ارزیابی (۳ سطح)</t>
         </is>
       </c>
     </row>
@@ -776,15 +809,19 @@
         <v/>
       </c>
       <c r="S31" s="8">
-        <f>AVERAGE(F31,I31,L31,O31,R31)</f>
+        <f>(MIN(0.4, 0.1*F31 + 0.3*I31) + MIN(0.5, 0.5*L31 + MAX(0, 0.1*F31 + 0.3*I31 - 0.4)) + MIN(0.1, 0.1*O31))</f>
         <v/>
       </c>
       <c r="T31" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S31)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F31 + 0.3*I31) + MIN(0.5, 0.5*L31 + MAX(0, 0.1*F31 + 0.3*I31 - 0.4)) + MIN(0.1, 0.1*O31)), 1)</f>
         <v/>
       </c>
       <c r="U31" s="10">
-        <f>RANK(T31, $T$31:$T$62)</f>
+        <f>IF(T31&gt;70, RANK(T31, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V31" s="10">
+        <f>IF(T31&lt;=70, "ضعیف", IF(T31&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -861,15 +898,19 @@
         <v/>
       </c>
       <c r="S32" s="8">
-        <f>AVERAGE(F32,I32,L32,O32,R32)</f>
+        <f>(MIN(0.4, 0.1*F32 + 0.3*I32) + MIN(0.5, 0.5*L32 + MAX(0, 0.1*F32 + 0.3*I32 - 0.4)) + MIN(0.1, 0.1*O32))</f>
         <v/>
       </c>
       <c r="T32" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S32)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F32 + 0.3*I32) + MIN(0.5, 0.5*L32 + MAX(0, 0.1*F32 + 0.3*I32 - 0.4)) + MIN(0.1, 0.1*O32)), 1)</f>
         <v/>
       </c>
       <c r="U32" s="10">
-        <f>RANK(T32, $T$31:$T$62)</f>
+        <f>IF(T32&gt;70, RANK(T32, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V32" s="10">
+        <f>IF(T32&lt;=70, "ضعیف", IF(T32&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -946,15 +987,19 @@
         <v/>
       </c>
       <c r="S33" s="8">
-        <f>AVERAGE(F33,I33,L33,O33,R33)</f>
+        <f>(MIN(0.4, 0.1*F33 + 0.3*I33) + MIN(0.5, 0.5*L33 + MAX(0, 0.1*F33 + 0.3*I33 - 0.4)) + MIN(0.1, 0.1*O33))</f>
         <v/>
       </c>
       <c r="T33" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S33)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F33 + 0.3*I33) + MIN(0.5, 0.5*L33 + MAX(0, 0.1*F33 + 0.3*I33 - 0.4)) + MIN(0.1, 0.1*O33)), 1)</f>
         <v/>
       </c>
       <c r="U33" s="10">
-        <f>RANK(T33, $T$31:$T$62)</f>
+        <f>IF(T33&gt;70, RANK(T33, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V33" s="10">
+        <f>IF(T33&lt;=70, "ضعیف", IF(T33&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1031,15 +1076,19 @@
         <v/>
       </c>
       <c r="S34" s="8">
-        <f>AVERAGE(F34,I34,L34,O34,R34)</f>
+        <f>(MIN(0.4, 0.1*F34 + 0.3*I34) + MIN(0.5, 0.5*L34 + MAX(0, 0.1*F34 + 0.3*I34 - 0.4)) + MIN(0.1, 0.1*O34))</f>
         <v/>
       </c>
       <c r="T34" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S34)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F34 + 0.3*I34) + MIN(0.5, 0.5*L34 + MAX(0, 0.1*F34 + 0.3*I34 - 0.4)) + MIN(0.1, 0.1*O34)), 1)</f>
         <v/>
       </c>
       <c r="U34" s="10">
-        <f>RANK(T34, $T$31:$T$62)</f>
+        <f>IF(T34&gt;70, RANK(T34, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V34" s="10">
+        <f>IF(T34&lt;=70, "ضعیف", IF(T34&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1116,15 +1165,19 @@
         <v/>
       </c>
       <c r="S35" s="8">
-        <f>AVERAGE(F35,I35,L35,O35,R35)</f>
+        <f>(MIN(0.4, 0.1*F35 + 0.3*I35) + MIN(0.5, 0.5*L35 + MAX(0, 0.1*F35 + 0.3*I35 - 0.4)) + MIN(0.1, 0.1*O35))</f>
         <v/>
       </c>
       <c r="T35" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S35)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F35 + 0.3*I35) + MIN(0.5, 0.5*L35 + MAX(0, 0.1*F35 + 0.3*I35 - 0.4)) + MIN(0.1, 0.1*O35)), 1)</f>
         <v/>
       </c>
       <c r="U35" s="10">
-        <f>RANK(T35, $T$31:$T$62)</f>
+        <f>IF(T35&gt;70, RANK(T35, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V35" s="10">
+        <f>IF(T35&lt;=70, "ضعیف", IF(T35&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1201,15 +1254,19 @@
         <v/>
       </c>
       <c r="S36" s="8">
-        <f>AVERAGE(F36,I36,L36,O36,R36)</f>
+        <f>(MIN(0.4, 0.1*F36 + 0.3*I36) + MIN(0.5, 0.5*L36 + MAX(0, 0.1*F36 + 0.3*I36 - 0.4)) + MIN(0.1, 0.1*O36))</f>
         <v/>
       </c>
       <c r="T36" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S36)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F36 + 0.3*I36) + MIN(0.5, 0.5*L36 + MAX(0, 0.1*F36 + 0.3*I36 - 0.4)) + MIN(0.1, 0.1*O36)), 1)</f>
         <v/>
       </c>
       <c r="U36" s="10">
-        <f>RANK(T36, $T$31:$T$62)</f>
+        <f>IF(T36&gt;70, RANK(T36, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V36" s="10">
+        <f>IF(T36&lt;=70, "ضعیف", IF(T36&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1286,15 +1343,19 @@
         <v/>
       </c>
       <c r="S37" s="8">
-        <f>AVERAGE(F37,I37,L37,O37,R37)</f>
+        <f>(MIN(0.4, 0.1*F37 + 0.3*I37) + MIN(0.5, 0.5*L37 + MAX(0, 0.1*F37 + 0.3*I37 - 0.4)) + MIN(0.1, 0.1*O37))</f>
         <v/>
       </c>
       <c r="T37" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S37)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F37 + 0.3*I37) + MIN(0.5, 0.5*L37 + MAX(0, 0.1*F37 + 0.3*I37 - 0.4)) + MIN(0.1, 0.1*O37)), 1)</f>
         <v/>
       </c>
       <c r="U37" s="10">
-        <f>RANK(T37, $T$31:$T$62)</f>
+        <f>IF(T37&gt;70, RANK(T37, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V37" s="10">
+        <f>IF(T37&lt;=70, "ضعیف", IF(T37&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1371,15 +1432,19 @@
         <v/>
       </c>
       <c r="S38" s="8">
-        <f>AVERAGE(F38,I38,L38,O38,R38)</f>
+        <f>(MIN(0.4, 0.1*F38 + 0.3*I38) + MIN(0.5, 0.5*L38 + MAX(0, 0.1*F38 + 0.3*I38 - 0.4)) + MIN(0.1, 0.1*O38))</f>
         <v/>
       </c>
       <c r="T38" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S38)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F38 + 0.3*I38) + MIN(0.5, 0.5*L38 + MAX(0, 0.1*F38 + 0.3*I38 - 0.4)) + MIN(0.1, 0.1*O38)), 1)</f>
         <v/>
       </c>
       <c r="U38" s="10">
-        <f>RANK(T38, $T$31:$T$62)</f>
+        <f>IF(T38&gt;70, RANK(T38, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V38" s="10">
+        <f>IF(T38&lt;=70, "ضعیف", IF(T38&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1456,15 +1521,19 @@
         <v/>
       </c>
       <c r="S39" s="8">
-        <f>AVERAGE(F39,I39,L39,O39,R39)</f>
+        <f>(MIN(0.4, 0.1*F39 + 0.3*I39) + MIN(0.5, 0.5*L39 + MAX(0, 0.1*F39 + 0.3*I39 - 0.4)) + MIN(0.1, 0.1*O39))</f>
         <v/>
       </c>
       <c r="T39" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S39)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F39 + 0.3*I39) + MIN(0.5, 0.5*L39 + MAX(0, 0.1*F39 + 0.3*I39 - 0.4)) + MIN(0.1, 0.1*O39)), 1)</f>
         <v/>
       </c>
       <c r="U39" s="10">
-        <f>RANK(T39, $T$31:$T$62)</f>
+        <f>IF(T39&gt;70, RANK(T39, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V39" s="10">
+        <f>IF(T39&lt;=70, "ضعیف", IF(T39&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1541,15 +1610,19 @@
         <v/>
       </c>
       <c r="S40" s="8">
-        <f>AVERAGE(F40,I40,L40,O40,R40)</f>
+        <f>(MIN(0.4, 0.1*F40 + 0.3*I40) + MIN(0.5, 0.5*L40 + MAX(0, 0.1*F40 + 0.3*I40 - 0.4)) + MIN(0.1, 0.1*O40))</f>
         <v/>
       </c>
       <c r="T40" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S40)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F40 + 0.3*I40) + MIN(0.5, 0.5*L40 + MAX(0, 0.1*F40 + 0.3*I40 - 0.4)) + MIN(0.1, 0.1*O40)), 1)</f>
         <v/>
       </c>
       <c r="U40" s="10">
-        <f>RANK(T40, $T$31:$T$62)</f>
+        <f>IF(T40&gt;70, RANK(T40, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V40" s="10">
+        <f>IF(T40&lt;=70, "ضعیف", IF(T40&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1626,15 +1699,19 @@
         <v/>
       </c>
       <c r="S41" s="8">
-        <f>AVERAGE(F41,I41,L41,O41,R41)</f>
+        <f>(MIN(0.4, 0.1*F41 + 0.3*I41) + MIN(0.5, 0.5*L41 + MAX(0, 0.1*F41 + 0.3*I41 - 0.4)) + MIN(0.1, 0.1*O41))</f>
         <v/>
       </c>
       <c r="T41" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S41)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F41 + 0.3*I41) + MIN(0.5, 0.5*L41 + MAX(0, 0.1*F41 + 0.3*I41 - 0.4)) + MIN(0.1, 0.1*O41)), 1)</f>
         <v/>
       </c>
       <c r="U41" s="10">
-        <f>RANK(T41, $T$31:$T$62)</f>
+        <f>IF(T41&gt;70, RANK(T41, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V41" s="10">
+        <f>IF(T41&lt;=70, "ضعیف", IF(T41&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1711,15 +1788,19 @@
         <v/>
       </c>
       <c r="S42" s="8">
-        <f>AVERAGE(F42,I42,L42,O42,R42)</f>
+        <f>(MIN(0.4, 0.1*F42 + 0.3*I42) + MIN(0.5, 0.5*L42 + MAX(0, 0.1*F42 + 0.3*I42 - 0.4)) + MIN(0.1, 0.1*O42))</f>
         <v/>
       </c>
       <c r="T42" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S42)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F42 + 0.3*I42) + MIN(0.5, 0.5*L42 + MAX(0, 0.1*F42 + 0.3*I42 - 0.4)) + MIN(0.1, 0.1*O42)), 1)</f>
         <v/>
       </c>
       <c r="U42" s="10">
-        <f>RANK(T42, $T$31:$T$62)</f>
+        <f>IF(T42&gt;70, RANK(T42, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V42" s="10">
+        <f>IF(T42&lt;=70, "ضعیف", IF(T42&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1796,15 +1877,19 @@
         <v/>
       </c>
       <c r="S43" s="8">
-        <f>AVERAGE(F43,I43,L43,O43,R43)</f>
+        <f>(MIN(0.4, 0.1*F43 + 0.3*I43) + MIN(0.5, 0.5*L43 + MAX(0, 0.1*F43 + 0.3*I43 - 0.4)) + MIN(0.1, 0.1*O43))</f>
         <v/>
       </c>
       <c r="T43" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S43)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F43 + 0.3*I43) + MIN(0.5, 0.5*L43 + MAX(0, 0.1*F43 + 0.3*I43 - 0.4)) + MIN(0.1, 0.1*O43)), 1)</f>
         <v/>
       </c>
       <c r="U43" s="10">
-        <f>RANK(T43, $T$31:$T$62)</f>
+        <f>IF(T43&gt;70, RANK(T43, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V43" s="10">
+        <f>IF(T43&lt;=70, "ضعیف", IF(T43&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1881,15 +1966,19 @@
         <v/>
       </c>
       <c r="S44" s="8">
-        <f>AVERAGE(F44,I44,L44,O44,R44)</f>
+        <f>(MIN(0.4, 0.1*F44 + 0.3*I44) + MIN(0.5, 0.5*L44 + MAX(0, 0.1*F44 + 0.3*I44 - 0.4)) + MIN(0.1, 0.1*O44))</f>
         <v/>
       </c>
       <c r="T44" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S44)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F44 + 0.3*I44) + MIN(0.5, 0.5*L44 + MAX(0, 0.1*F44 + 0.3*I44 - 0.4)) + MIN(0.1, 0.1*O44)), 1)</f>
         <v/>
       </c>
       <c r="U44" s="10">
-        <f>RANK(T44, $T$31:$T$62)</f>
+        <f>IF(T44&gt;70, RANK(T44, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V44" s="10">
+        <f>IF(T44&lt;=70, "ضعیف", IF(T44&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -1966,15 +2055,19 @@
         <v/>
       </c>
       <c r="S45" s="8">
-        <f>AVERAGE(F45,I45,L45,O45,R45)</f>
+        <f>(MIN(0.4, 0.1*F45 + 0.3*I45) + MIN(0.5, 0.5*L45 + MAX(0, 0.1*F45 + 0.3*I45 - 0.4)) + MIN(0.1, 0.1*O45))</f>
         <v/>
       </c>
       <c r="T45" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S45)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F45 + 0.3*I45) + MIN(0.5, 0.5*L45 + MAX(0, 0.1*F45 + 0.3*I45 - 0.4)) + MIN(0.1, 0.1*O45)), 1)</f>
         <v/>
       </c>
       <c r="U45" s="10">
-        <f>RANK(T45, $T$31:$T$62)</f>
+        <f>IF(T45&gt;70, RANK(T45, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V45" s="10">
+        <f>IF(T45&lt;=70, "ضعیف", IF(T45&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2051,15 +2144,19 @@
         <v/>
       </c>
       <c r="S46" s="8">
-        <f>AVERAGE(F46,I46,L46,O46,R46)</f>
+        <f>(MIN(0.4, 0.1*F46 + 0.3*I46) + MIN(0.5, 0.5*L46 + MAX(0, 0.1*F46 + 0.3*I46 - 0.4)) + MIN(0.1, 0.1*O46))</f>
         <v/>
       </c>
       <c r="T46" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S46)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F46 + 0.3*I46) + MIN(0.5, 0.5*L46 + MAX(0, 0.1*F46 + 0.3*I46 - 0.4)) + MIN(0.1, 0.1*O46)), 1)</f>
         <v/>
       </c>
       <c r="U46" s="10">
-        <f>RANK(T46, $T$31:$T$62)</f>
+        <f>IF(T46&gt;70, RANK(T46, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V46" s="10">
+        <f>IF(T46&lt;=70, "ضعیف", IF(T46&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2136,15 +2233,19 @@
         <v/>
       </c>
       <c r="S47" s="8">
-        <f>AVERAGE(F47,I47,L47,O47,R47)</f>
+        <f>(MIN(0.4, 0.1*F47 + 0.3*I47) + MIN(0.5, 0.5*L47 + MAX(0, 0.1*F47 + 0.3*I47 - 0.4)) + MIN(0.1, 0.1*O47))</f>
         <v/>
       </c>
       <c r="T47" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S47)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F47 + 0.3*I47) + MIN(0.5, 0.5*L47 + MAX(0, 0.1*F47 + 0.3*I47 - 0.4)) + MIN(0.1, 0.1*O47)), 1)</f>
         <v/>
       </c>
       <c r="U47" s="10">
-        <f>RANK(T47, $T$31:$T$62)</f>
+        <f>IF(T47&gt;70, RANK(T47, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V47" s="10">
+        <f>IF(T47&lt;=70, "ضعیف", IF(T47&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2221,15 +2322,19 @@
         <v/>
       </c>
       <c r="S48" s="8">
-        <f>AVERAGE(F48,I48,L48,O48,R48)</f>
+        <f>(MIN(0.4, 0.1*F48 + 0.3*I48) + MIN(0.5, 0.5*L48 + MAX(0, 0.1*F48 + 0.3*I48 - 0.4)) + MIN(0.1, 0.1*O48))</f>
         <v/>
       </c>
       <c r="T48" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S48)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F48 + 0.3*I48) + MIN(0.5, 0.5*L48 + MAX(0, 0.1*F48 + 0.3*I48 - 0.4)) + MIN(0.1, 0.1*O48)), 1)</f>
         <v/>
       </c>
       <c r="U48" s="10">
-        <f>RANK(T48, $T$31:$T$62)</f>
+        <f>IF(T48&gt;70, RANK(T48, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V48" s="10">
+        <f>IF(T48&lt;=70, "ضعیف", IF(T48&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2306,15 +2411,19 @@
         <v/>
       </c>
       <c r="S49" s="8">
-        <f>AVERAGE(F49,I49,L49,O49,R49)</f>
+        <f>(MIN(0.4, 0.1*F49 + 0.3*I49) + MIN(0.5, 0.5*L49 + MAX(0, 0.1*F49 + 0.3*I49 - 0.4)) + MIN(0.1, 0.1*O49))</f>
         <v/>
       </c>
       <c r="T49" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S49)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F49 + 0.3*I49) + MIN(0.5, 0.5*L49 + MAX(0, 0.1*F49 + 0.3*I49 - 0.4)) + MIN(0.1, 0.1*O49)), 1)</f>
         <v/>
       </c>
       <c r="U49" s="10">
-        <f>RANK(T49, $T$31:$T$62)</f>
+        <f>IF(T49&gt;70, RANK(T49, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V49" s="10">
+        <f>IF(T49&lt;=70, "ضعیف", IF(T49&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2391,15 +2500,19 @@
         <v/>
       </c>
       <c r="S50" s="8">
-        <f>AVERAGE(F50,I50,L50,O50,R50)</f>
+        <f>(MIN(0.4, 0.1*F50 + 0.3*I50) + MIN(0.5, 0.5*L50 + MAX(0, 0.1*F50 + 0.3*I50 - 0.4)) + MIN(0.1, 0.1*O50))</f>
         <v/>
       </c>
       <c r="T50" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S50)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F50 + 0.3*I50) + MIN(0.5, 0.5*L50 + MAX(0, 0.1*F50 + 0.3*I50 - 0.4)) + MIN(0.1, 0.1*O50)), 1)</f>
         <v/>
       </c>
       <c r="U50" s="10">
-        <f>RANK(T50, $T$31:$T$62)</f>
+        <f>IF(T50&gt;70, RANK(T50, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V50" s="10">
+        <f>IF(T50&lt;=70, "ضعیف", IF(T50&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2476,15 +2589,19 @@
         <v/>
       </c>
       <c r="S51" s="8">
-        <f>AVERAGE(F51,I51,L51,O51,R51)</f>
+        <f>(MIN(0.4, 0.1*F51 + 0.3*I51) + MIN(0.5, 0.5*L51 + MAX(0, 0.1*F51 + 0.3*I51 - 0.4)) + MIN(0.1, 0.1*O51))</f>
         <v/>
       </c>
       <c r="T51" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S51)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F51 + 0.3*I51) + MIN(0.5, 0.5*L51 + MAX(0, 0.1*F51 + 0.3*I51 - 0.4)) + MIN(0.1, 0.1*O51)), 1)</f>
         <v/>
       </c>
       <c r="U51" s="10">
-        <f>RANK(T51, $T$31:$T$62)</f>
+        <f>IF(T51&gt;70, RANK(T51, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V51" s="10">
+        <f>IF(T51&lt;=70, "ضعیف", IF(T51&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2561,15 +2678,19 @@
         <v/>
       </c>
       <c r="S52" s="8">
-        <f>AVERAGE(F52,I52,L52,O52,R52)</f>
+        <f>(MIN(0.4, 0.1*F52 + 0.3*I52) + MIN(0.5, 0.5*L52 + MAX(0, 0.1*F52 + 0.3*I52 - 0.4)) + MIN(0.1, 0.1*O52))</f>
         <v/>
       </c>
       <c r="T52" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S52)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F52 + 0.3*I52) + MIN(0.5, 0.5*L52 + MAX(0, 0.1*F52 + 0.3*I52 - 0.4)) + MIN(0.1, 0.1*O52)), 1)</f>
         <v/>
       </c>
       <c r="U52" s="10">
-        <f>RANK(T52, $T$31:$T$62)</f>
+        <f>IF(T52&gt;70, RANK(T52, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V52" s="10">
+        <f>IF(T52&lt;=70, "ضعیف", IF(T52&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2646,15 +2767,19 @@
         <v/>
       </c>
       <c r="S53" s="8">
-        <f>AVERAGE(F53,I53,L53,O53,R53)</f>
+        <f>(MIN(0.4, 0.1*F53 + 0.3*I53) + MIN(0.5, 0.5*L53 + MAX(0, 0.1*F53 + 0.3*I53 - 0.4)) + MIN(0.1, 0.1*O53))</f>
         <v/>
       </c>
       <c r="T53" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S53)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F53 + 0.3*I53) + MIN(0.5, 0.5*L53 + MAX(0, 0.1*F53 + 0.3*I53 - 0.4)) + MIN(0.1, 0.1*O53)), 1)</f>
         <v/>
       </c>
       <c r="U53" s="10">
-        <f>RANK(T53, $T$31:$T$62)</f>
+        <f>IF(T53&gt;70, RANK(T53, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V53" s="10">
+        <f>IF(T53&lt;=70, "ضعیف", IF(T53&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2731,15 +2856,19 @@
         <v/>
       </c>
       <c r="S54" s="8">
-        <f>AVERAGE(F54,I54,L54,O54,R54)</f>
+        <f>(MIN(0.4, 0.1*F54 + 0.3*I54) + MIN(0.5, 0.5*L54 + MAX(0, 0.1*F54 + 0.3*I54 - 0.4)) + MIN(0.1, 0.1*O54))</f>
         <v/>
       </c>
       <c r="T54" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S54)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F54 + 0.3*I54) + MIN(0.5, 0.5*L54 + MAX(0, 0.1*F54 + 0.3*I54 - 0.4)) + MIN(0.1, 0.1*O54)), 1)</f>
         <v/>
       </c>
       <c r="U54" s="10">
-        <f>RANK(T54, $T$31:$T$62)</f>
+        <f>IF(T54&gt;70, RANK(T54, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V54" s="10">
+        <f>IF(T54&lt;=70, "ضعیف", IF(T54&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2816,15 +2945,19 @@
         <v/>
       </c>
       <c r="S55" s="8">
-        <f>AVERAGE(F55,I55,L55,O55,R55)</f>
+        <f>(MIN(0.4, 0.1*F55 + 0.3*I55) + MIN(0.5, 0.5*L55 + MAX(0, 0.1*F55 + 0.3*I55 - 0.4)) + MIN(0.1, 0.1*O55))</f>
         <v/>
       </c>
       <c r="T55" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S55)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F55 + 0.3*I55) + MIN(0.5, 0.5*L55 + MAX(0, 0.1*F55 + 0.3*I55 - 0.4)) + MIN(0.1, 0.1*O55)), 1)</f>
         <v/>
       </c>
       <c r="U55" s="10">
-        <f>RANK(T55, $T$31:$T$62)</f>
+        <f>IF(T55&gt;70, RANK(T55, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V55" s="10">
+        <f>IF(T55&lt;=70, "ضعیف", IF(T55&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2901,15 +3034,19 @@
         <v/>
       </c>
       <c r="S56" s="8">
-        <f>AVERAGE(F56,I56,L56,O56,R56)</f>
+        <f>(MIN(0.4, 0.1*F56 + 0.3*I56) + MIN(0.5, 0.5*L56 + MAX(0, 0.1*F56 + 0.3*I56 - 0.4)) + MIN(0.1, 0.1*O56))</f>
         <v/>
       </c>
       <c r="T56" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S56)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F56 + 0.3*I56) + MIN(0.5, 0.5*L56 + MAX(0, 0.1*F56 + 0.3*I56 - 0.4)) + MIN(0.1, 0.1*O56)), 1)</f>
         <v/>
       </c>
       <c r="U56" s="10">
-        <f>RANK(T56, $T$31:$T$62)</f>
+        <f>IF(T56&gt;70, RANK(T56, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V56" s="10">
+        <f>IF(T56&lt;=70, "ضعیف", IF(T56&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -2986,15 +3123,19 @@
         <v/>
       </c>
       <c r="S57" s="8">
-        <f>AVERAGE(F57,I57,L57,O57,R57)</f>
+        <f>(MIN(0.4, 0.1*F57 + 0.3*I57) + MIN(0.5, 0.5*L57 + MAX(0, 0.1*F57 + 0.3*I57 - 0.4)) + MIN(0.1, 0.1*O57))</f>
         <v/>
       </c>
       <c r="T57" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S57)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F57 + 0.3*I57) + MIN(0.5, 0.5*L57 + MAX(0, 0.1*F57 + 0.3*I57 - 0.4)) + MIN(0.1, 0.1*O57)), 1)</f>
         <v/>
       </c>
       <c r="U57" s="10">
-        <f>RANK(T57, $T$31:$T$62)</f>
+        <f>IF(T57&gt;70, RANK(T57, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V57" s="10">
+        <f>IF(T57&lt;=70, "ضعیف", IF(T57&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -3071,15 +3212,19 @@
         <v/>
       </c>
       <c r="S58" s="8">
-        <f>AVERAGE(F58,I58,L58,O58,R58)</f>
+        <f>(MIN(0.4, 0.1*F58 + 0.3*I58) + MIN(0.5, 0.5*L58 + MAX(0, 0.1*F58 + 0.3*I58 - 0.4)) + MIN(0.1, 0.1*O58))</f>
         <v/>
       </c>
       <c r="T58" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S58)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F58 + 0.3*I58) + MIN(0.5, 0.5*L58 + MAX(0, 0.1*F58 + 0.3*I58 - 0.4)) + MIN(0.1, 0.1*O58)), 1)</f>
         <v/>
       </c>
       <c r="U58" s="10">
-        <f>RANK(T58, $T$31:$T$62)</f>
+        <f>IF(T58&gt;70, RANK(T58, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V58" s="10">
+        <f>IF(T58&lt;=70, "ضعیف", IF(T58&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -3156,15 +3301,19 @@
         <v/>
       </c>
       <c r="S59" s="8">
-        <f>AVERAGE(F59,I59,L59,O59,R59)</f>
+        <f>(MIN(0.4, 0.1*F59 + 0.3*I59) + MIN(0.5, 0.5*L59 + MAX(0, 0.1*F59 + 0.3*I59 - 0.4)) + MIN(0.1, 0.1*O59))</f>
         <v/>
       </c>
       <c r="T59" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S59)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F59 + 0.3*I59) + MIN(0.5, 0.5*L59 + MAX(0, 0.1*F59 + 0.3*I59 - 0.4)) + MIN(0.1, 0.1*O59)), 1)</f>
         <v/>
       </c>
       <c r="U59" s="10">
-        <f>RANK(T59, $T$31:$T$62)</f>
+        <f>IF(T59&gt;70, RANK(T59, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V59" s="10">
+        <f>IF(T59&lt;=70, "ضعیف", IF(T59&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -3241,15 +3390,19 @@
         <v/>
       </c>
       <c r="S60" s="8">
-        <f>AVERAGE(F60,I60,L60,O60,R60)</f>
+        <f>(MIN(0.4, 0.1*F60 + 0.3*I60) + MIN(0.5, 0.5*L60 + MAX(0, 0.1*F60 + 0.3*I60 - 0.4)) + MIN(0.1, 0.1*O60))</f>
         <v/>
       </c>
       <c r="T60" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S60)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F60 + 0.3*I60) + MIN(0.5, 0.5*L60 + MAX(0, 0.1*F60 + 0.3*I60 - 0.4)) + MIN(0.1, 0.1*O60)), 1)</f>
         <v/>
       </c>
       <c r="U60" s="10">
-        <f>RANK(T60, $T$31:$T$62)</f>
+        <f>IF(T60&gt;70, RANK(T60, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V60" s="10">
+        <f>IF(T60&lt;=70, "ضعیف", IF(T60&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -3326,15 +3479,19 @@
         <v/>
       </c>
       <c r="S61" s="8">
-        <f>AVERAGE(F61,I61,L61,O61,R61)</f>
+        <f>(MIN(0.4, 0.1*F61 + 0.3*I61) + MIN(0.5, 0.5*L61 + MAX(0, 0.1*F61 + 0.3*I61 - 0.4)) + MIN(0.1, 0.1*O61))</f>
         <v/>
       </c>
       <c r="T61" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S61)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F61 + 0.3*I61) + MIN(0.5, 0.5*L61 + MAX(0, 0.1*F61 + 0.3*I61 - 0.4)) + MIN(0.1, 0.1*O61)), 1)</f>
         <v/>
       </c>
       <c r="U61" s="10">
-        <f>RANK(T61, $T$31:$T$62)</f>
+        <f>IF(T61&gt;70, RANK(T61, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V61" s="10">
+        <f>IF(T61&lt;=70, "ضعیف", IF(T61&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -3411,15 +3568,19 @@
         <v/>
       </c>
       <c r="S62" s="8">
-        <f>AVERAGE(F62,I62,L62,O62,R62)</f>
+        <f>(MIN(0.4, 0.1*F62 + 0.3*I62) + MIN(0.5, 0.5*L62 + MAX(0, 0.1*F62 + 0.3*I62 - 0.4)) + MIN(0.1, 0.1*O62))</f>
         <v/>
       </c>
       <c r="T62" s="9">
-        <f>ROUND(70 + 30 * MIN(1, MAX(0, S62)), 1)</f>
+        <f>ROUND(70 + 30 * (MIN(0.4, 0.1*F62 + 0.3*I62) + MIN(0.5, 0.5*L62 + MAX(0, 0.1*F62 + 0.3*I62 - 0.4)) + MIN(0.1, 0.1*O62)), 1)</f>
         <v/>
       </c>
       <c r="U62" s="10">
-        <f>RANK(T62, $T$31:$T$62)</f>
+        <f>IF(T62&gt;70, RANK(T62, $T$31:$T$62), "-")</f>
+        <v/>
+      </c>
+      <c r="V62" s="10">
+        <f>IF(T62&lt;=70, "ضعیف", IF(T62&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -3437,12 +3598,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="112" customWidth="1" min="3" max="3"/>
+    <col width="101" customWidth="1" min="3" max="3"/>
     <col width="73" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
@@ -3484,7 +3645,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>۱۴۰۵</t>
         </is>
       </c>
     </row>
@@ -3605,14 +3766,15 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>درصد میانگین تحقق:</t>
+          <t>درصد تحقق وزنی اهداف:</t>
         </is>
       </c>
       <c r="C11" s="17">
-        <f>AVERAGE(E5:E9)</f>
+        <f>(MIN(0.4, 0.1*E5 + 0.3*E6) + MIN(0.5, 0.5*E7 + MAX(0, 0.1*E5 + 0.3*E6 - 0.4)) + MIN(0.1, 0.1*E8))</f>
         <v/>
       </c>
     </row>
@@ -3641,11 +3803,11 @@
     <row r="14">
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>سطح ارزیابی عملکرد ۳ ماهه:</t>
+          <t>سطح ارزیابی (۳ سطح):</t>
         </is>
       </c>
       <c r="C14" s="20">
-        <f>IF(C12&gt;=100, "عالی (پیشتاز)", IF(C12&gt;=92.5, "خوب", IF(C12&gt;=85, "متوسط", IF(C12&gt;70, "ضعیف", "فاقد عملکرد"))))</f>
+        <f>IF(C12&lt;=70, "ضعیف", IF(C12&gt;=90, "عالی", "متوسط"))</f>
         <v/>
       </c>
     </row>
@@ -4390,22 +4552,22 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>'کارنامه هوشمند ۳ ماهه'!C3</f>
@@ -4506,22 +4668,22 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4">
         <f>'کارنامه هوشمند ۳ ماهه'!C3</f>

--- a/تهیه کارنامه ۳ ماهه نواحی.xlsx
+++ b/تهیه کارنامه ۳ ماهه نواحی.xlsx
@@ -4582,16 +4582,16 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>1500</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F26" s="14" t="n">
         <v>3</v>
